--- a/Backend/data/plantilla_baterias.xlsx
+++ b/Backend/data/plantilla_baterias.xlsx
@@ -554,9 +554,21 @@
           <t>2024-11-25 00:00:00</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-491</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -619,9 +631,21 @@
           <t>2024-11-25 00:00:00</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-491</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,9 +708,21 @@
           <t>2024-11-25 00:00:00</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-491</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,9 +785,21 @@
           <t>2029-12-07 00:00:00</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3 AÑOS 8 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -814,9 +862,21 @@
           <t>2029-12-07 00:00:00</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3 AÑOS 8 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,9 +939,21 @@
           <t>2029-12-07 00:00:00</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3 AÑOS 8 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -944,9 +1016,21 @@
           <t>2025-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-289</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 16 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1009,9 +1093,21 @@
           <t>2025-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-289</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 16 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1074,9 +1170,21 @@
           <t>2023-11-09 00:00:00</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-873</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1139,9 +1247,21 @@
           <t>2026-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 15 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1204,9 +1324,21 @@
           <t>2029-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3 AÑOS 8 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1269,9 +1401,21 @@
           <t>2029-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3 AÑOS 8 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1334,9 +1478,21 @@
           <t>2029-01-19 00:00:00</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1399,9 +1555,21 @@
           <t>2029-01-19 00:00:00</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1464,9 +1632,21 @@
           <t>2029-01-19 00:00:00</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1529,9 +1709,21 @@
           <t>2023-11-09 00:00:00</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-873</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1594,9 +1786,21 @@
           <t>2023-11-09 00:00:00</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-873</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1659,9 +1863,21 @@
           <t>2023-11-09 00:00:00</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-873</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1724,9 +1940,21 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-876</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1789,9 +2017,21 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-876</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1854,9 +2094,21 @@
           <t>2024-11-28 00:00:00</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-488</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1919,9 +2171,21 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-876</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1984,9 +2248,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2049,9 +2325,21 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-876</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2114,9 +2402,21 @@
           <t>2029-02-22 00:00:00</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2179,9 +2479,21 @@
           <t>2029-02-22 00:00:00</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2244,9 +2556,21 @@
           <t>2029-02-22 00:00:00</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2309,9 +2633,21 @@
           <t>2026-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0 AÑOS 6 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2374,9 +2710,21 @@
           <t>2026-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0 AÑOS 6 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2439,9 +2787,21 @@
           <t>2026-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0 AÑOS 6 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2504,9 +2864,21 @@
           <t>2026-05-09 00:00:00</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2569,9 +2941,21 @@
           <t>2026-05-09 00:00:00</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2634,9 +3018,21 @@
           <t>2026-05-09 00:00:00</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2699,9 +3095,21 @@
           <t>2026-05-03 00:00:00</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2764,9 +3172,21 @@
           <t>2026-05-03 00:00:00</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2829,9 +3249,21 @@
           <t>2026-05-03 00:00:00</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2894,9 +3326,21 @@
           <t>2024-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-494</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2959,9 +3403,21 @@
           <t>2024-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-494</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3024,9 +3480,21 @@
           <t>2024-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-494</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3089,9 +3557,21 @@
           <t>2026-03-13 00:00:00</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3154,9 +3634,21 @@
           <t>2026-03-13 00:00:00</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3219,9 +3711,21 @@
           <t>2026-03-13 00:00:00</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3284,9 +3788,21 @@
           <t>2024-11-30 00:00:00</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-486</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3349,9 +3865,21 @@
           <t>2024-11-30 00:00:00</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-486</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3414,9 +3942,21 @@
           <t>2029-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 5 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3479,9 +4019,21 @@
           <t>2029-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 5 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3544,9 +4096,21 @@
           <t>2029-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 5 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3609,9 +4173,21 @@
           <t>2024-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-495</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3674,9 +4250,21 @@
           <t>2024-11-21 00:00:00</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-495</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3739,9 +4327,21 @@
           <t>2026-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3804,9 +4404,21 @@
           <t>2026-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3869,9 +4481,21 @@
           <t>2024-10-25 00:00:00</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-522</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3934,9 +4558,21 @@
           <t>2024-10-25 00:00:00</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-522</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3999,9 +4635,21 @@
           <t>2026-01-18 00:00:00</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>-72</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4064,9 +4712,21 @@
           <t>2026-01-18 00:00:00</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>-72</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4129,9 +4789,21 @@
           <t>2026-01-18 00:00:00</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-72</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4194,9 +4866,21 @@
           <t>2028-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4259,9 +4943,21 @@
           <t>2028-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4324,9 +5020,21 @@
           <t>2028-07-07 00:00:00</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4389,9 +5097,21 @@
           <t>2024-10-14 00:00:00</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>-533</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 17 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4454,9 +5174,21 @@
           <t>2024-10-14 00:00:00</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>-533</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 17 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4519,9 +5251,21 @@
           <t>2028-07-25 00:00:00</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 24 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4584,9 +5328,21 @@
           <t>2028-07-25 00:00:00</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 24 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4649,9 +5405,21 @@
           <t>2025-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>-291</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4714,9 +5482,21 @@
           <t>2025-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>-291</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4779,9 +5559,21 @@
           <t>2025-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>-284</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4844,9 +5636,21 @@
           <t>2024-11-23 00:00:00</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>-493</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4909,9 +5713,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4974,9 +5790,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5039,9 +5867,21 @@
           <t>2026-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5104,9 +5944,21 @@
           <t>2026-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5169,9 +6021,21 @@
           <t>2023-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>-1094</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 29 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5234,9 +6098,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5299,9 +6175,21 @@
           <t>2024-05-30 00:00:00</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>-670</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5364,9 +6252,21 @@
           <t>2025-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>-289</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 16 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5429,9 +6329,21 @@
           <t>2028-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5494,9 +6406,21 @@
           <t>2028-04-09 00:00:00</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5559,9 +6483,21 @@
           <t>2028-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5624,9 +6560,21 @@
           <t>2028-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5689,9 +6637,21 @@
           <t>2025-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>-289</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 16 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5754,9 +6714,21 @@
           <t>2024-06-29 00:00:00</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>-640</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1 AÑOS 9 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5819,9 +6791,21 @@
           <t>2026-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5884,9 +6868,21 @@
           <t>2023-08-22 00:00:00</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>-952</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5949,9 +6945,21 @@
           <t>2023-08-22 00:00:00</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>-952</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6014,9 +7022,21 @@
           <t>2026-05-07 00:00:00</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6079,9 +7099,21 @@
           <t>2026-05-07 00:00:00</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6144,9 +7176,21 @@
           <t>2025-05-04 00:00:00</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>-331</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6209,9 +7253,21 @@
           <t>2025-05-04 00:00:00</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>-331</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6274,9 +7330,21 @@
           <t>2026-01-19 00:00:00</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>-71</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 12 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6339,9 +7407,21 @@
           <t>2026-01-19 00:00:00</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>-71</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0 AÑOS 2 MESES 12 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6404,9 +7484,21 @@
           <t>2025-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>-112</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6469,9 +7561,21 @@
           <t>2025-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>-112</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6534,9 +7638,21 @@
           <t>2025-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>-112</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6599,9 +7715,21 @@
           <t>2024-04-03 00:00:00</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>-727</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1 AÑOS 11 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6664,9 +7792,21 @@
           <t>2024-04-03 00:00:00</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>-727</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1 AÑOS 11 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6729,9 +7869,21 @@
           <t>2024-10-26 00:00:00</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>-521</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 5 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6794,9 +7946,21 @@
           <t>2024-10-26 00:00:00</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>-521</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 5 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6859,9 +8023,21 @@
           <t>2025-06-14 00:00:00</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>-290</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 17 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6924,9 +8100,21 @@
           <t>2024-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>-520</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6989,9 +8177,21 @@
           <t>2024-02-29 00:00:00</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>-761</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7054,9 +8254,21 @@
           <t>2024-02-29 00:00:00</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>-761</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7119,9 +8331,21 @@
           <t>2023-06-06 00:00:00</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>-1029</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2 AÑOS 9 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7184,9 +8408,21 @@
           <t>2024-10-15 00:00:00</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>-532</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 16 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7249,9 +8485,21 @@
           <t>2024-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>-519</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7314,9 +8562,21 @@
           <t>2024-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>-519</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7379,9 +8639,21 @@
           <t>2024-10-21 00:00:00</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>-526</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7444,9 +8716,21 @@
           <t>2024-10-21 00:00:00</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>-526</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7509,9 +8793,21 @@
           <t>2024-10-29 00:00:00</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>-518</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7574,9 +8870,21 @@
           <t>2024-10-29 00:00:00</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>-518</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7639,9 +8947,21 @@
           <t>2026-05-09 00:00:00</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7704,9 +9024,21 @@
           <t>2026-05-09 00:00:00</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7769,9 +9101,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7834,9 +9178,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7899,9 +9255,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7964,9 +9332,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8029,9 +9409,21 @@
           <t>2024-05-28 00:00:00</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-672</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8094,9 +9486,21 @@
           <t>2024-05-28 00:00:00</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-672</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8159,9 +9563,21 @@
           <t>2025-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>-291</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8224,9 +9640,21 @@
           <t>2025-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-291</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 18 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8289,9 +9717,21 @@
           <t>2024-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-519</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8354,9 +9794,21 @@
           <t>2025-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-327</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 23 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8419,9 +9871,21 @@
           <t>2025-05-08 00:00:00</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-327</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 23 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8484,9 +9948,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8549,9 +10025,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8614,9 +10102,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8679,9 +10179,21 @@
           <t>2024-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-519</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 3 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8744,9 +10256,21 @@
           <t>2026-12-21 00:00:00</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>0 AÑOS 8 MESES 20 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8809,9 +10333,21 @@
           <t>2029-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8874,9 +10410,21 @@
           <t>2024-06-29 00:00:00</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>-640</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>1 AÑOS 9 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8939,9 +10487,21 @@
           <t>2024-05-27 00:00:00</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>-673</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9004,9 +10564,21 @@
           <t>2024-05-27 00:00:00</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>-673</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9069,9 +10641,21 @@
           <t>2026-04-11 00:00:00</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9134,9 +10718,21 @@
           <t>2026-04-11 00:00:00</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9199,9 +10795,21 @@
           <t>2024-05-17 00:00:00</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>-683</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9264,9 +10872,21 @@
           <t>2024-11-23 00:00:00</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>-493</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9329,9 +10949,21 @@
           <t>2023-12-05 00:00:00</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>-847</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9394,9 +11026,21 @@
           <t>2024-10-25 00:00:00</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>-522</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9459,9 +11103,21 @@
           <t>2024-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-511</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9524,9 +11180,21 @@
           <t>2024-11-25 00:00:00</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>-491</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9589,9 +11257,21 @@
           <t>2025-08-03 00:00:00</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>-240</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>0 AÑOS 7 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9654,9 +11334,21 @@
           <t>2024-03-02 00:00:00</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>-759</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 29 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9719,9 +11411,21 @@
           <t>2024-05-17 00:00:00</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>-683</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9784,9 +11488,21 @@
           <t>2024-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>-494</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9849,9 +11565,21 @@
           <t>2024-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>-494</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9914,9 +11642,21 @@
           <t>2024-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>-492</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9979,9 +11719,21 @@
           <t>2026-05-03 00:00:00</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10044,9 +11796,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10109,9 +11873,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10174,9 +11950,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10239,9 +12027,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10304,9 +12104,21 @@
           <t>2024-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>-760</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>2 AÑOS 0 MESES 30 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10369,9 +12181,21 @@
           <t>2027-06-28 00:00:00</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>1 AÑOS 2 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10434,9 +12258,21 @@
           <t>2027-06-28 00:00:00</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>1 AÑOS 2 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10499,9 +12335,21 @@
           <t>2027-06-28 00:00:00</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>1 AÑOS 2 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10564,9 +12412,21 @@
           <t>2027-07-05 00:00:00</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10629,9 +12489,21 @@
           <t>2027-07-05 00:00:00</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10694,9 +12566,21 @@
           <t>2027-07-05 00:00:00</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10759,9 +12643,21 @@
           <t>2024-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-520</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10824,9 +12720,21 @@
           <t>2024-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>-520</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10889,9 +12797,21 @@
           <t>2024-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-520</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10954,9 +12874,21 @@
           <t>2024-11-04 00:00:00</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-512</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11019,9 +12951,21 @@
           <t>2024-11-04 00:00:00</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-512</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11084,9 +13028,21 @@
           <t>2024-11-04 00:00:00</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-512</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11149,9 +13105,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11214,9 +13182,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11275,9 +13255,21 @@
           <t>2025-06-12 00:00:00</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>-292</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 19 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11340,9 +13332,21 @@
           <t>2026-05-15 00:00:00</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11405,9 +13409,21 @@
           <t>2026-05-15 00:00:00</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11470,9 +13486,21 @@
           <t>2026-05-15 00:00:00</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11535,9 +13563,21 @@
           <t>2028-08-31 00:00:00</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2 AÑOS 5 MESES 0 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11600,9 +13640,21 @@
           <t>2026-05-16 00:00:00</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 15 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11665,9 +13717,21 @@
           <t>2027-07-26 00:00:00</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11730,9 +13794,21 @@
           <t>2027-07-26 00:00:00</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 25 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11795,9 +13871,21 @@
           <t>2029-03-09 00:00:00</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11860,9 +13948,21 @@
           <t>2029-03-09 00:00:00</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 6 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11925,9 +14025,21 @@
           <t>2027-07-14 00:00:00</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11990,9 +14102,21 @@
           <t>2027-07-14 00:00:00</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>1 AÑOS 3 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12055,9 +14179,21 @@
           <t>2025-06-23 00:00:00</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-281</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12120,9 +14256,21 @@
           <t>2025-06-23 00:00:00</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-281</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12185,9 +14333,21 @@
           <t>2027-10-21 00:00:00</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>1 AÑOS 6 MESES 20 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12250,9 +14410,21 @@
           <t>2025-05-04 00:00:00</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>-331</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12315,9 +14487,21 @@
           <t>2025-05-04 00:00:00</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-331</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 27 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12380,9 +14564,21 @@
           <t>2029-03-03 00:00:00</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 0 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12445,9 +14641,21 @@
           <t>2029-03-03 00:00:00</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 0 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12510,9 +14718,21 @@
           <t>2029-03-03 00:00:00</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES 0 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12575,9 +14795,21 @@
           <t>2027-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12640,9 +14872,21 @@
           <t>2027-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12705,9 +14949,21 @@
           <t>2027-12-09 00:00:00</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 8 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12770,9 +15026,21 @@
           <t>2025-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>-284</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12835,9 +15103,21 @@
           <t>2025-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-284</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12900,9 +15180,21 @@
           <t>2025-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-284</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12965,9 +15257,21 @@
           <t>2028-12-15 00:00:00</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>2 AÑOS 8 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13030,9 +15334,21 @@
           <t>2028-12-15 00:00:00</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>2 AÑOS 8 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13095,9 +15411,21 @@
           <t>2028-12-15 00:00:00</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>2 AÑOS 8 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13160,9 +15488,21 @@
           <t>2024-10-21 00:00:00</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-526</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13225,9 +15565,21 @@
           <t>2024-10-21 00:00:00</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-526</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13290,9 +15642,21 @@
           <t>2026-05-10 00:00:00</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>0 AÑOS 1 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13355,9 +15719,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13420,9 +15796,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13485,9 +15873,21 @@
           <t>2026-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13550,9 +15950,21 @@
           <t>2029-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES -2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13615,9 +16027,21 @@
           <t>2029-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES -2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13680,9 +16104,21 @@
           <t>2029-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>2 AÑOS 11 MESES -2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13745,9 +16181,21 @@
           <t>2028-08-13 00:00:00</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13810,9 +16258,21 @@
           <t>2028-08-13 00:00:00</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13875,9 +16335,21 @@
           <t>2028-08-13 00:00:00</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>2 AÑOS 4 MESES 13 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13940,9 +16412,21 @@
           <t>2026-03-27 00:00:00</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14005,9 +16489,21 @@
           <t>2026-03-27 00:00:00</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14070,9 +16566,21 @@
           <t>2026-03-27 00:00:00</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>0 AÑOS 0 MESES 4 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14135,9 +16643,21 @@
           <t>2028-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14200,9 +16720,21 @@
           <t>2028-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14265,9 +16797,21 @@
           <t>2028-07-29 00:00:00</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>2 AÑOS 3 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14330,9 +16874,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14395,9 +16951,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14460,9 +17028,21 @@
           <t>2024-07-09 00:00:00</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-630</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>1 AÑOS 8 MESES 22 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14525,9 +17105,21 @@
           <t>2024-09-24 00:00:00</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-553</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>1 AÑOS 6 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14590,9 +17182,21 @@
           <t>2024-09-24 00:00:00</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-553</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>1 AÑOS 6 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14655,9 +17259,21 @@
           <t>2024-09-24 00:00:00</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-553</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>1 AÑOS 6 MESES 7 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14720,9 +17336,21 @@
           <t>2025-12-21 00:00:00</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14785,9 +17413,21 @@
           <t>2025-12-21 00:00:00</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14850,9 +17490,21 @@
           <t>2025-12-21 00:00:00</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>0 AÑOS 3 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14915,9 +17567,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14980,9 +17644,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15045,9 +17721,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15110,9 +17798,21 @@
           <t>2025-05-30 00:00:00</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-305</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15175,9 +17875,21 @@
           <t>2025-05-30 00:00:00</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-305</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15240,9 +17952,21 @@
           <t>2025-05-30 00:00:00</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-305</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>0 AÑOS 10 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15305,9 +18029,21 @@
           <t>2026-08-09 00:00:00</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>0 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15370,9 +18106,21 @@
           <t>2026-08-09 00:00:00</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>0 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15435,9 +18183,21 @@
           <t>2026-08-09 00:00:00</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>0 AÑOS 4 MESES 9 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15500,9 +18260,21 @@
           <t>2024-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-527</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15561,9 +18333,21 @@
           <t>2024-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-527</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15626,9 +18410,21 @@
           <t>2024-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-527</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>1 AÑOS 5 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15691,9 +18487,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15756,9 +18564,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15821,9 +18641,21 @@
           <t>2025-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>-299</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>0 AÑOS 9 MESES 26 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15886,9 +18718,21 @@
           <t>2029-02-24 00:00:00</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 24 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15951,9 +18795,21 @@
           <t>2029-02-24 00:00:00</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>2 AÑOS 10 MESES 24 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16016,9 +18872,21 @@
           <t>2024-05-17 00:00:00</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-683</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16081,9 +18949,21 @@
           <t>2024-05-17 00:00:00</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-683</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>1 AÑOS 10 MESES 14 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16146,9 +19026,21 @@
           <t>2024-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>-513</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16211,9 +19103,21 @@
           <t>2024-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>-513</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>1 AÑOS 4 MESES 28 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -16276,9 +19180,21 @@
           <t>2024-08-30 00:00:00</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>-578</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>1 AÑOS 7 MESES 1 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16337,9 +19253,21 @@
           <t>2026-12-11 00:00:00</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>0 AÑOS 8 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16402,9 +19330,21 @@
           <t>2023-08-20 00:00:00</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-954</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16467,9 +19407,21 @@
           <t>2023-08-20 00:00:00</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-954</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>2 AÑOS 7 MESES 11 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16553,9 +19505,21 @@
           <t>2025-02-21 00:00:00</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-403</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>1 AÑOS 1 MESES 10 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16618,9 +19582,21 @@
           <t>2024-02-29 00:00:00</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-761</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>2 AÑOS 1 MESES 2 DIAS</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16690,12 +19666,12 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>-823.0</t>
+          <t>-827</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2 AÑOS 3 MESES 2 DIAS</t>
+          <t>2 AÑOS 3 MESES 6 DIAS</t>
         </is>
       </c>
     </row>
@@ -16767,12 +19743,12 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>3 AÑOS 0 MESES 0 DIAS</t>
+          <t>1 AÑOS 9 MESES 1 DIAS</t>
         </is>
       </c>
     </row>
@@ -16844,12 +19820,12 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>365</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>3 AÑOS 0 MESES 0 DIAS</t>
+          <t>1 AÑOS 0 MESES 0 DIAS</t>
         </is>
       </c>
     </row>
@@ -16921,12 +19897,12 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>365</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>3 AÑOS 0 MESES 0 DIAS</t>
+          <t>1 AÑOS 0 MESES 0 DIAS</t>
         </is>
       </c>
     </row>
